--- a/output/summary_WB_regions_quality_mean_only.xlsx
+++ b/output/summary_WB_regions_quality_mean_only.xlsx
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>240.7100538993762</v>
+        <v>244.9677449457553</v>
       </c>
     </row>
     <row r="27">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>262.5094469312979</v>
+        <v>274.7406237796313</v>
       </c>
     </row>
     <row r="28">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>257.0735620118609</v>
+        <v>269.50243626433</v>
       </c>
     </row>
     <row r="29">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>260.5961777657237</v>
+        <v>275.4331363625215</v>
       </c>
     </row>
     <row r="30">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>262.6118530619801</v>
+        <v>269.1750146291828</v>
       </c>
     </row>
     <row r="31">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>246.317784701006</v>
+        <v>255.6514551452244</v>
       </c>
     </row>
     <row r="32">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>193.8617153625563</v>
+        <v>185.4158425590985</v>
       </c>
     </row>
     <row r="33">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>236.8301941902613</v>
+        <v>229.7314483656197</v>
       </c>
     </row>
     <row r="34">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>251.7686268659554</v>
+        <v>263.4621234459282</v>
       </c>
     </row>
     <row r="35">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>273.0054578034059</v>
+        <v>285.7620598900472</v>
       </c>
     </row>
     <row r="36">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>228.7274034518673</v>
+        <v>239.80760757511</v>
       </c>
     </row>
     <row r="37">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>287.2086118192463</v>
+        <v>301.0712691161417</v>
       </c>
     </row>
     <row r="38">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>241.9958812090776</v>
+        <v>255.7715174652351</v>
       </c>
     </row>
     <row r="39">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>279.7147171978049</v>
+        <v>295.6425687789092</v>
       </c>
     </row>
     <row r="40">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>235.3968460827077</v>
+        <v>241.1728884601391</v>
       </c>
     </row>
     <row r="41">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>287.7754384754278</v>
+        <v>295.0663875084739</v>
       </c>
     </row>
     <row r="42">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>229.3893691172059</v>
+        <v>238.085987319424</v>
       </c>
     </row>
     <row r="43">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>263.1150629240188</v>
+        <v>273.0808506327567</v>
       </c>
     </row>
     <row r="44">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>182.7794600716317</v>
+        <v>174.8198180184403</v>
       </c>
     </row>
     <row r="45">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>204.4086559494204</v>
+        <v>195.5000391737348</v>
       </c>
     </row>
     <row r="46">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>214.7510439718039</v>
+        <v>208.3358244354318</v>
       </c>
     </row>
     <row r="47">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>259.1041153487595</v>
+        <v>251.315813517475</v>
       </c>
     </row>
     <row r="48">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>224.3638346361114</v>
+        <v>228.4132148072067</v>
       </c>
     </row>
     <row r="49">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>256.8414782192161</v>
+        <v>261.3047428643323</v>
       </c>
     </row>
     <row r="50">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="F74">
-        <v>232.5085799987827</v>
+        <v>237.0693881444009</v>
       </c>
     </row>
     <row r="75">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>262.5094469312979</v>
+        <v>274.7406237796313</v>
       </c>
     </row>
     <row r="76">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>257.0735620118609</v>
+        <v>269.50243626433</v>
       </c>
     </row>
     <row r="77">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>260.5961777657237</v>
+        <v>275.4331363625215</v>
       </c>
     </row>
     <row r="78">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>256.7807718370167</v>
+        <v>262.9796814997947</v>
       </c>
     </row>
     <row r="79">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F79">
-        <v>246.317784701006</v>
+        <v>255.6514551452244</v>
       </c>
     </row>
     <row r="80">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>168.5852952740319</v>
+        <v>161.2417743034581</v>
       </c>
     </row>
     <row r="81">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>224.4894347299565</v>
+        <v>217.8090452542897</v>
       </c>
     </row>
     <row r="82">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>251.7686268659554</v>
+        <v>263.4621234459282</v>
       </c>
     </row>
     <row r="83">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="F83">
-        <v>273.0054578034059</v>
+        <v>285.7620598900472</v>
       </c>
     </row>
     <row r="84">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>228.7274034518673</v>
+        <v>239.80760757511</v>
       </c>
     </row>
     <row r="85">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>287.2086118192463</v>
+        <v>301.0712691161417</v>
       </c>
     </row>
     <row r="86">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>241.9958812090776</v>
+        <v>255.7715174652351</v>
       </c>
     </row>
     <row r="87">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>279.7147171978049</v>
+        <v>295.6425687789092</v>
       </c>
     </row>
     <row r="88">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>229.9106763384574</v>
+        <v>235.3448696459168</v>
       </c>
     </row>
     <row r="89">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>281.6254446184889</v>
+        <v>288.5314276007315</v>
       </c>
     </row>
     <row r="90">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>229.3893691172059</v>
+        <v>238.085987319424</v>
       </c>
     </row>
     <row r="91">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>263.1150629240188</v>
+        <v>273.0808506327567</v>
       </c>
     </row>
     <row r="92">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>158.9459987578705</v>
+        <v>152.0251022699541</v>
       </c>
     </row>
     <row r="93">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>177.7589774340498</v>
+        <v>170.013246336374</v>
       </c>
     </row>
     <row r="94">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>203.6343297107727</v>
+        <v>197.5960835252783</v>
       </c>
     </row>
     <row r="95">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>245.528512790179</v>
+        <v>238.2003153655523</v>
       </c>
     </row>
     <row r="96">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>216.8033373887203</v>
+        <v>221.1326834119451</v>
       </c>
     </row>
     <row r="97">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>248.0074503191084</v>
+        <v>252.7966790952215</v>
       </c>
     </row>
     <row r="98">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="F122">
-        <v>134.9462157461386</v>
+        <v>137.2199529911969</v>
       </c>
     </row>
     <row r="123">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="F123">
-        <v>144.9857682648383</v>
+        <v>151.6817392654643</v>
       </c>
     </row>
     <row r="124">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="F124">
-        <v>140.3950815447106</v>
+        <v>147.1553491123449</v>
       </c>
     </row>
     <row r="125">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="F125">
-        <v>147.8326122249773</v>
+        <v>156.225414821453</v>
       </c>
     </row>
     <row r="126">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="F126">
-        <v>149.1809042788445</v>
+        <v>152.8777824739762</v>
       </c>
     </row>
     <row r="127">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F127">
-        <v>134.3593686686727</v>
+        <v>139.4497514624218</v>
       </c>
     </row>
     <row r="128">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F128">
-        <v>110.0561573330575</v>
+        <v>105.2572493082924</v>
       </c>
     </row>
     <row r="129">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="F129">
-        <v>137.7279723190343</v>
+        <v>133.5787943795237</v>
       </c>
     </row>
     <row r="130">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="F130">
-        <v>138.6454823147478</v>
+        <v>145.0237877440875</v>
       </c>
     </row>
     <row r="131">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="F131">
-        <v>151.1815438070763</v>
+        <v>158.1879400144952</v>
       </c>
     </row>
     <row r="132">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="F132">
-        <v>124.3690621136518</v>
+        <v>130.3661387741059</v>
       </c>
     </row>
     <row r="133">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F133">
-        <v>157.4324833763179</v>
+        <v>165.004105891811</v>
       </c>
     </row>
     <row r="134">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="F134">
-        <v>137.1026520602698</v>
+        <v>144.8835713991253</v>
       </c>
     </row>
     <row r="135">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="F135">
-        <v>158.8615313547813</v>
+        <v>167.8832655466761</v>
       </c>
     </row>
     <row r="136">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="F136">
-        <v>134.0142186015434</v>
+        <v>137.2760451306754</v>
       </c>
     </row>
     <row r="137">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="F137">
-        <v>163.2043506358615</v>
+        <v>167.3034870323228</v>
       </c>
     </row>
     <row r="138">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F138">
-        <v>124.8678990634468</v>
+        <v>129.6010277609471</v>
       </c>
     </row>
     <row r="139">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="F139">
-        <v>143.7773118255515</v>
+        <v>149.2221812173699</v>
       </c>
     </row>
     <row r="140">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>103.76957266782</v>
+        <v>99.24621136242902</v>
       </c>
     </row>
     <row r="141">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="F141">
-        <v>116.0390762622802</v>
+        <v>110.977931463334</v>
       </c>
     </row>
     <row r="142">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="F142">
-        <v>124.9365189617383</v>
+        <v>121.1824765497022</v>
       </c>
     </row>
     <row r="143">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F143">
-        <v>150.6322653178118</v>
+        <v>146.0844661678465</v>
       </c>
     </row>
     <row r="144">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="F144">
-        <v>125.5587300814795</v>
+        <v>127.7106207564888</v>
       </c>
     </row>
     <row r="145">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="F145">
-        <v>144.2103466203254</v>
+        <v>146.6043293295946</v>
       </c>
     </row>
   </sheetData>

--- a/output/summary_WB_regions_quality_mean_only.xlsx
+++ b/output/summary_WB_regions_quality_mean_only.xlsx
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>203.2934705330083</v>
+        <v>205.4423293716456</v>
       </c>
     </row>
     <row r="3">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="F3">
-        <v>220.0117514159871</v>
+        <v>222.2547489332221</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>221.9093356017447</v>
+        <v>224.9519005721748</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>227.7027862917564</v>
+        <v>230.4356321178711</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>233.2520330594974</v>
+        <v>235.3157350041162</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>198.6952364618872</v>
+        <v>201.2230953542665</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>157.5416274832345</v>
+        <v>158.8942941805615</v>
       </c>
     </row>
     <row r="9">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>203.9835671674258</v>
+        <v>206.0921930371581</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>211.1952229777032</v>
+        <v>213.6030932611299</v>
       </c>
     </row>
     <row r="11">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>228.6273299080877</v>
+        <v>230.7092125071003</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>197.8471890736684</v>
+        <v>201.0282311307386</v>
       </c>
     </row>
     <row r="13">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>247.4900146401943</v>
+        <v>250.385363405146</v>
       </c>
     </row>
     <row r="14">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="F14">
-        <v>211.4642472948236</v>
+        <v>214.1853723386369</v>
       </c>
     </row>
     <row r="15">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>244.39376469561</v>
+        <v>247.1386578693536</v>
       </c>
     </row>
     <row r="16">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F16">
-        <v>209.5169386791599</v>
+        <v>211.5811355002117</v>
       </c>
     </row>
     <row r="17">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>255.1980158472566</v>
+        <v>257.2612602183975</v>
       </c>
     </row>
     <row r="18">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>185.0608151930446</v>
+        <v>187.7408159714768</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>212.2240375672713</v>
+        <v>214.6009331532056</v>
       </c>
     </row>
     <row r="20">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>148.5026156921848</v>
+        <v>149.8733938489133</v>
       </c>
     </row>
     <row r="21">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>166.1440209330802</v>
+        <v>167.4794510227642</v>
       </c>
     </row>
     <row r="22">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="F22">
-        <v>184.9702062347645</v>
+        <v>186.9982104740173</v>
       </c>
     </row>
     <row r="23">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>223.1646542193233</v>
+        <v>225.3546129222136</v>
       </c>
     </row>
     <row r="24">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>189.5638131056606</v>
+        <v>191.7877356995985</v>
       </c>
     </row>
     <row r="25">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>216.8427155394305</v>
+        <v>218.9174969863301</v>
       </c>
     </row>
     <row r="26">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>244.9677449457553</v>
+        <v>247.5484616980287</v>
       </c>
     </row>
     <row r="27">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>274.7406237796313</v>
+        <v>277.5001470091651</v>
       </c>
     </row>
     <row r="28">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>269.50243626433</v>
+        <v>273.1911041451213</v>
       </c>
     </row>
     <row r="29">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>275.4331363625215</v>
+        <v>278.7329514534464</v>
       </c>
     </row>
     <row r="30">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>269.1750146291828</v>
+        <v>271.5517565693888</v>
       </c>
     </row>
     <row r="31">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>255.6514551452244</v>
+        <v>258.9032181470266</v>
       </c>
     </row>
     <row r="32">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>185.4158425590985</v>
+        <v>187.0072808078066</v>
       </c>
     </row>
     <row r="33">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>229.7314483656197</v>
+        <v>232.1081678656959</v>
       </c>
     </row>
     <row r="34">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>263.4621234459282</v>
+        <v>266.4149295467641</v>
       </c>
     </row>
     <row r="35">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>285.7620598900472</v>
+        <v>288.332705631062</v>
       </c>
     </row>
     <row r="36">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>239.80760757511</v>
+        <v>243.6553601063086</v>
       </c>
     </row>
     <row r="37">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>301.0712691161417</v>
+        <v>304.5908127096516</v>
       </c>
     </row>
     <row r="38">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>255.7715174652351</v>
+        <v>259.0578649060102</v>
       </c>
     </row>
     <row r="39">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>295.6425687789092</v>
+        <v>298.9562267566762</v>
       </c>
     </row>
     <row r="40">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>241.1728884601391</v>
+        <v>243.5505142898121</v>
       </c>
     </row>
     <row r="41">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>295.0663875084739</v>
+        <v>297.4423121853187</v>
       </c>
     </row>
     <row r="42">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>238.085987319424</v>
+        <v>241.5333798480976</v>
       </c>
     </row>
     <row r="43">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>273.0808506327567</v>
+        <v>276.1384995678744</v>
       </c>
     </row>
     <row r="44">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>174.8198180184403</v>
+        <v>176.4326739840571</v>
       </c>
     </row>
     <row r="45">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>195.5000391737348</v>
+        <v>197.0710942619934</v>
       </c>
     </row>
     <row r="46">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>208.3358244354318</v>
+        <v>210.6214011523071</v>
       </c>
     </row>
     <row r="47">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>251.315813517475</v>
+        <v>253.7844798156433</v>
       </c>
     </row>
     <row r="48">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>228.4132148072067</v>
+        <v>231.0834009087349</v>
       </c>
     </row>
     <row r="49">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>261.3047428643323</v>
+        <v>263.7971659253734</v>
       </c>
     </row>
     <row r="50">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>196.5169887909223</v>
+        <v>198.6052689339755</v>
       </c>
     </row>
     <row r="51">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>220.0117514159871</v>
+        <v>222.2547489332221</v>
       </c>
     </row>
     <row r="52">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>221.9093356017447</v>
+        <v>224.9519005721748</v>
       </c>
     </row>
     <row r="53">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>227.7027862917564</v>
+        <v>230.4356321178711</v>
       </c>
     </row>
     <row r="54">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F54">
-        <v>227.3912796189027</v>
+        <v>229.4041266420748</v>
       </c>
     </row>
     <row r="55">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>198.6952364618872</v>
+        <v>201.2230953542665</v>
       </c>
     </row>
     <row r="56">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="F56">
-        <v>137.0030125997827</v>
+        <v>138.1793153409385</v>
       </c>
     </row>
     <row r="57">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>193.6447662511655</v>
+        <v>195.6479584136895</v>
       </c>
     </row>
     <row r="58">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F58">
-        <v>211.1952229777032</v>
+        <v>213.6030932611299</v>
       </c>
     </row>
     <row r="59">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="F59">
-        <v>228.6273299080877</v>
+        <v>230.7092125071003</v>
       </c>
     </row>
     <row r="60">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F60">
-        <v>197.8471890736684</v>
+        <v>201.0282311307386</v>
       </c>
     </row>
     <row r="61">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F61">
-        <v>247.4900146401943</v>
+        <v>250.385363405146</v>
       </c>
     </row>
     <row r="62">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F62">
-        <v>211.4642472948236</v>
+        <v>214.1853723386369</v>
       </c>
     </row>
     <row r="63">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="F63">
-        <v>244.39376469561</v>
+        <v>247.1386578693536</v>
       </c>
     </row>
     <row r="64">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F64">
-        <v>203.9979976393313</v>
+        <v>206.0105794645407</v>
       </c>
     </row>
     <row r="65">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="F65">
-        <v>249.0212152511862</v>
+        <v>251.0343074821435</v>
       </c>
     </row>
     <row r="66">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="F66">
-        <v>185.0608151930446</v>
+        <v>187.7408159714768</v>
       </c>
     </row>
     <row r="67">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="F67">
-        <v>212.2240375672713</v>
+        <v>214.6009331532056</v>
       </c>
     </row>
     <row r="68">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>129.1403456917309</v>
+        <v>130.3323933768629</v>
       </c>
     </row>
     <row r="69">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="F69">
-        <v>144.4858830585996</v>
+        <v>145.6472013959224</v>
       </c>
     </row>
     <row r="70">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="F70">
-        <v>175.6633854702153</v>
+        <v>177.5906856566514</v>
       </c>
     </row>
     <row r="71">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="F71">
-        <v>211.7847695516999</v>
+        <v>213.8645231704046</v>
       </c>
     </row>
     <row r="72">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="F72">
-        <v>183.3197918059108</v>
+        <v>185.4839201990257</v>
       </c>
     </row>
     <row r="73">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>209.54077006836</v>
+        <v>211.5541986334455</v>
       </c>
     </row>
     <row r="74">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="F74">
-        <v>237.0693881444009</v>
+        <v>239.5795043065802</v>
       </c>
     </row>
     <row r="75">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>274.7406237796313</v>
+        <v>277.5001470091651</v>
       </c>
     </row>
     <row r="76">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>269.50243626433</v>
+        <v>273.1911041451213</v>
       </c>
     </row>
     <row r="77">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>275.4331363625215</v>
+        <v>278.7329514534464</v>
       </c>
     </row>
     <row r="78">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>262.9796814997947</v>
+        <v>265.3026111676061</v>
       </c>
     </row>
     <row r="79">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F79">
-        <v>255.6514551452244</v>
+        <v>258.9032181470266</v>
       </c>
     </row>
     <row r="80">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>161.2417743034581</v>
+        <v>162.6257066400563</v>
       </c>
     </row>
     <row r="81">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>217.8090452542897</v>
+        <v>220.0638959476481</v>
       </c>
     </row>
     <row r="82">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>263.4621234459282</v>
+        <v>266.4149295467641</v>
       </c>
     </row>
     <row r="83">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="F83">
-        <v>285.7620598900472</v>
+        <v>288.332705631062</v>
       </c>
     </row>
     <row r="84">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>239.80760757511</v>
+        <v>243.6553601063086</v>
       </c>
     </row>
     <row r="85">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>301.0712691161417</v>
+        <v>304.5908127096516</v>
       </c>
     </row>
     <row r="86">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>255.7715174652351</v>
+        <v>259.0578649060102</v>
       </c>
     </row>
     <row r="87">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>295.6425687789092</v>
+        <v>298.9562267566762</v>
       </c>
     </row>
     <row r="88">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>235.3448696459168</v>
+        <v>237.6679373476579</v>
       </c>
     </row>
     <row r="89">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>288.5314276007315</v>
+        <v>290.85422963938</v>
       </c>
     </row>
     <row r="90">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>238.085987319424</v>
+        <v>241.5333798480976</v>
       </c>
     </row>
     <row r="91">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>273.0808506327567</v>
+        <v>276.1384995678744</v>
       </c>
     </row>
     <row r="92">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>152.0251022699541</v>
+        <v>153.427654430497</v>
       </c>
     </row>
     <row r="93">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>170.013246336374</v>
+        <v>171.3794582567097</v>
       </c>
     </row>
     <row r="94">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>197.5960835252783</v>
+        <v>199.7652437605324</v>
       </c>
     </row>
     <row r="95">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>238.2003153655523</v>
+        <v>240.5416124342901</v>
       </c>
     </row>
     <row r="96">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>221.1326834119451</v>
+        <v>223.7331727988306</v>
       </c>
     </row>
     <row r="97">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>252.7966790952215</v>
+        <v>255.2176095679521</v>
       </c>
     </row>
     <row r="98">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="F98">
-        <v>113.9544634893662</v>
+        <v>115.248956720007</v>
       </c>
     </row>
     <row r="99">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="F99">
-        <v>121.4164502649449</v>
+        <v>122.7187063431167</v>
       </c>
     </row>
     <row r="100">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="F100">
-        <v>121.1556420067288</v>
+        <v>122.8088409401229</v>
       </c>
     </row>
     <row r="101">
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="F101">
-        <v>129.2229185480618</v>
+        <v>130.9315604456168</v>
       </c>
     </row>
     <row r="102">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="F102">
-        <v>132.5907690627994</v>
+        <v>133.9226267039411</v>
       </c>
     </row>
     <row r="103">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="F103">
-        <v>108.3784613020942</v>
+        <v>109.7628570366262</v>
       </c>
     </row>
     <row r="104">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>89.43772207136922</v>
+        <v>90.30512076170933</v>
       </c>
     </row>
     <row r="105">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F105">
-        <v>118.5962400016613</v>
+        <v>120.0085446546611</v>
       </c>
     </row>
     <row r="106">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="F106">
-        <v>116.2009766688983</v>
+        <v>117.5708565163258</v>
       </c>
     </row>
     <row r="107">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="F107">
-        <v>126.5130506394304</v>
+        <v>127.7492242571382</v>
       </c>
     </row>
     <row r="108">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="F108">
-        <v>107.5373243818202</v>
+        <v>109.2299438433055</v>
       </c>
     </row>
     <row r="109">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="F109">
-        <v>135.6333949287279</v>
+        <v>137.2446855529257</v>
       </c>
     </row>
     <row r="110">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F110">
-        <v>119.8540634484984</v>
+        <v>121.5345898855326</v>
       </c>
     </row>
     <row r="111">
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="F111">
-        <v>138.8528094000156</v>
+        <v>140.590350113188</v>
       </c>
     </row>
     <row r="112">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="F112">
-        <v>119.351669691951</v>
+        <v>120.6722382712564</v>
       </c>
     </row>
     <row r="113">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F113">
-        <v>144.8319273351157</v>
+        <v>146.1742230875528</v>
       </c>
     </row>
     <row r="114">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="F114">
-        <v>100.7335430597937</v>
+        <v>102.1818208891596</v>
       </c>
     </row>
     <row r="115">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="F115">
-        <v>115.9641575577435</v>
+        <v>117.2851660653326</v>
       </c>
     </row>
     <row r="116">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F116">
-        <v>84.31080393560521</v>
+        <v>85.18243625305477</v>
       </c>
     </row>
     <row r="117">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="F117">
-        <v>94.31699073574478</v>
+        <v>95.18036029912312</v>
       </c>
     </row>
     <row r="118">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="F118">
-        <v>107.5791896356873</v>
+        <v>108.9281787913259</v>
       </c>
     </row>
     <row r="119">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="F119">
-        <v>129.7104771359219</v>
+        <v>131.1866558231301</v>
       </c>
     </row>
     <row r="120">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F120">
-        <v>106.0634678045901</v>
+        <v>107.379733067185</v>
       </c>
     </row>
     <row r="121">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="F121">
-        <v>121.7417687767268</v>
+        <v>123.0147760674015</v>
       </c>
     </row>
     <row r="122">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="F122">
-        <v>137.2199529911969</v>
+        <v>138.7728710228168</v>
       </c>
     </row>
     <row r="123">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="F123">
-        <v>151.6817392654643</v>
+        <v>153.2898984319826</v>
       </c>
     </row>
     <row r="124">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="F124">
-        <v>147.1553491123449</v>
+        <v>149.1601803663034</v>
       </c>
     </row>
     <row r="125">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="F125">
-        <v>156.225414821453</v>
+        <v>158.286327158709</v>
       </c>
     </row>
     <row r="126">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="F126">
-        <v>152.8777824739762</v>
+        <v>154.4085958545948</v>
       </c>
     </row>
     <row r="127">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F127">
-        <v>139.4497514624218</v>
+        <v>141.2307805052833</v>
       </c>
     </row>
     <row r="128">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F128">
-        <v>105.2572493082924</v>
+        <v>106.2776397891987</v>
       </c>
     </row>
     <row r="129">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="F129">
-        <v>133.5787943795237</v>
+        <v>135.1709842672249</v>
       </c>
     </row>
     <row r="130">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="F130">
-        <v>145.0237877440875</v>
+        <v>146.7102227321197</v>
       </c>
     </row>
     <row r="131">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="F131">
-        <v>158.1879400144952</v>
+        <v>159.7196074542528</v>
       </c>
     </row>
     <row r="132">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="F132">
-        <v>130.3661387741059</v>
+        <v>132.4143096113699</v>
       </c>
     </row>
     <row r="133">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F133">
-        <v>165.004105891811</v>
+        <v>166.9628624545986</v>
       </c>
     </row>
     <row r="134">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="F134">
-        <v>144.8835713991253</v>
+        <v>146.9109535373512</v>
       </c>
     </row>
     <row r="135">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="F135">
-        <v>167.8832655466761</v>
+        <v>169.9786423039139</v>
       </c>
     </row>
     <row r="136">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="F136">
-        <v>137.2760451306754</v>
+        <v>138.7940916084226</v>
       </c>
     </row>
     <row r="137">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="F137">
-        <v>167.3034870323228</v>
+        <v>168.8461049680941</v>
       </c>
     </row>
     <row r="138">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F138">
-        <v>129.6010277609471</v>
+        <v>131.4641876879074</v>
       </c>
     </row>
     <row r="139">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="F139">
-        <v>149.2221812173699</v>
+        <v>150.9217156097676</v>
       </c>
     </row>
     <row r="140">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>99.24621136242902</v>
+        <v>100.2716361562998</v>
       </c>
     </row>
     <row r="141">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="F141">
-        <v>110.977931463334</v>
+        <v>111.9935308075682</v>
       </c>
     </row>
     <row r="142">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="F142">
-        <v>121.1824765497022</v>
+        <v>122.703253176281</v>
       </c>
     </row>
     <row r="143">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F143">
-        <v>146.0844661678465</v>
+        <v>147.748699287836</v>
       </c>
     </row>
     <row r="144">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="F144">
-        <v>127.7106207564888</v>
+        <v>129.2893964793354</v>
       </c>
     </row>
     <row r="145">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="F145">
-        <v>146.6043293295946</v>
+        <v>148.1317294489447</v>
       </c>
     </row>
   </sheetData>

--- a/output/summary_WB_regions_quality_mean_only.xlsx
+++ b/output/summary_WB_regions_quality_mean_only.xlsx
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>198.6052689339755</v>
+        <v>198.4147578321731</v>
       </c>
     </row>
     <row r="51">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>222.2547489332221</v>
+        <v>221.8260445142896</v>
       </c>
     </row>
     <row r="52">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>224.9519005721748</v>
+        <v>224.9337516464444</v>
       </c>
     </row>
     <row r="53">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>230.4356321178711</v>
+        <v>230.1741136826712</v>
       </c>
     </row>
     <row r="54">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F54">
-        <v>229.4041266420748</v>
+        <v>229.3846627839536</v>
       </c>
     </row>
     <row r="55">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="F56">
-        <v>138.1793153409385</v>
+        <v>138.7890091962096</v>
       </c>
     </row>
     <row r="57">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>195.6479584136895</v>
+        <v>194.3608927603723</v>
       </c>
     </row>
     <row r="58">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F58">
-        <v>213.6030932611299</v>
+        <v>213.1958780234546</v>
       </c>
     </row>
     <row r="59">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="F59">
-        <v>230.7092125071003</v>
+        <v>230.2595086971783</v>
       </c>
     </row>
     <row r="60">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F60">
-        <v>201.0282311307386</v>
+        <v>201.0120052063976</v>
       </c>
     </row>
     <row r="61">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F61">
-        <v>250.385363405146</v>
+        <v>250.3651701197706</v>
       </c>
     </row>
     <row r="62">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F62">
-        <v>214.1853723386369</v>
+        <v>213.9340093386497</v>
       </c>
     </row>
     <row r="63">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="F63">
-        <v>247.1386578693536</v>
+        <v>246.8667010474335</v>
       </c>
     </row>
     <row r="64">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F64">
-        <v>206.0105794645407</v>
+        <v>206.0081595397197</v>
       </c>
     </row>
     <row r="65">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="F65">
-        <v>251.0343074821435</v>
+        <v>250.9990844338183</v>
       </c>
     </row>
     <row r="66">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>130.3323933768629</v>
+        <v>130.9176177733322</v>
       </c>
     </row>
     <row r="69">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="F69">
-        <v>145.6472013959224</v>
+        <v>146.2801827428997</v>
       </c>
     </row>
     <row r="70">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="F70">
-        <v>177.5906856566514</v>
+        <v>176.4305397891598</v>
       </c>
     </row>
     <row r="71">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="F71">
-        <v>213.8645231704046</v>
+        <v>212.4494181100004</v>
       </c>
     </row>
     <row r="72">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="F72">
-        <v>185.4839201990257</v>
+        <v>185.3098393960044</v>
       </c>
     </row>
     <row r="73">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>211.5541986334455</v>
+        <v>211.3474731326388</v>
       </c>
     </row>
     <row r="74">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="F74">
-        <v>239.5795043065802</v>
+        <v>239.3690815816242</v>
       </c>
     </row>
     <row r="75">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>277.5001470091651</v>
+        <v>276.9776295916038</v>
       </c>
     </row>
     <row r="76">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>273.1911041451213</v>
+        <v>273.1706143819874</v>
       </c>
     </row>
     <row r="77">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>278.7329514534464</v>
+        <v>278.5014797052831</v>
       </c>
     </row>
     <row r="78">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>265.3026111676061</v>
+        <v>265.0785773807465</v>
       </c>
     </row>
     <row r="79">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>162.6257066400563</v>
+        <v>163.3368287992505</v>
       </c>
     </row>
     <row r="81">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>220.0638959476481</v>
+        <v>218.7374009283901</v>
       </c>
     </row>
     <row r="82">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>266.4149295467641</v>
+        <v>265.9182897247678</v>
       </c>
     </row>
     <row r="83">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="F83">
-        <v>288.332705631062</v>
+        <v>287.7849004307477</v>
       </c>
     </row>
     <row r="84">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>243.6553601063086</v>
+        <v>243.6370413721139</v>
       </c>
     </row>
     <row r="85">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>304.5908127096516</v>
+        <v>304.568014906609</v>
       </c>
     </row>
     <row r="86">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>259.0578649060102</v>
+        <v>258.8353836172741</v>
       </c>
     </row>
     <row r="87">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>298.9562267566762</v>
+        <v>298.7155140562228</v>
       </c>
     </row>
     <row r="88">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>237.6679373476579</v>
+        <v>237.4804903442172</v>
       </c>
     </row>
     <row r="89">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>290.85422963938</v>
+        <v>290.596366919452</v>
       </c>
     </row>
     <row r="90">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>153.427654430497</v>
+        <v>154.1101100305656</v>
       </c>
     </row>
     <row r="93">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>171.3794582567097</v>
+        <v>172.1178622721679</v>
       </c>
     </row>
     <row r="94">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>199.7652437605324</v>
+        <v>198.575761608398</v>
       </c>
     </row>
     <row r="95">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>240.5416124342901</v>
+        <v>239.0768958906612</v>
       </c>
     </row>
     <row r="96">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>223.7331727988306</v>
+        <v>223.5421224540177</v>
       </c>
     </row>
     <row r="97">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>255.2176095679521</v>
+        <v>254.9880690225915</v>
       </c>
     </row>
     <row r="98">

--- a/output/summary_WB_regions_quality_mean_only.xlsx
+++ b/output/summary_WB_regions_quality_mean_only.xlsx
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>205.4423293716456</v>
+        <v>203.2934705330083</v>
       </c>
     </row>
     <row r="3">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="F3">
-        <v>222.2547489332221</v>
+        <v>220.0117514159871</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>224.9519005721748</v>
+        <v>221.9093356017447</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>230.4356321178711</v>
+        <v>227.7027862917564</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>235.3157350041162</v>
+        <v>233.2520330594974</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>201.2230953542665</v>
+        <v>198.6952364618872</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>158.8942941805615</v>
+        <v>157.5416274832345</v>
       </c>
     </row>
     <row r="9">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>206.0921930371581</v>
+        <v>203.9835671674258</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>213.6030932611299</v>
+        <v>211.1952229777032</v>
       </c>
     </row>
     <row r="11">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>230.7092125071003</v>
+        <v>228.6273299080877</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>201.0282311307386</v>
+        <v>197.8471890736684</v>
       </c>
     </row>
     <row r="13">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>250.385363405146</v>
+        <v>247.4900146401943</v>
       </c>
     </row>
     <row r="14">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="F14">
-        <v>214.1853723386369</v>
+        <v>211.4642472948236</v>
       </c>
     </row>
     <row r="15">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>247.1386578693536</v>
+        <v>244.39376469561</v>
       </c>
     </row>
     <row r="16">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F16">
-        <v>211.5811355002117</v>
+        <v>209.5169386791599</v>
       </c>
     </row>
     <row r="17">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>257.2612602183975</v>
+        <v>255.1980158472566</v>
       </c>
     </row>
     <row r="18">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>187.7408159714768</v>
+        <v>185.0608151930446</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>214.6009331532056</v>
+        <v>212.2240375672713</v>
       </c>
     </row>
     <row r="20">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>149.8733938489133</v>
+        <v>148.5026156921848</v>
       </c>
     </row>
     <row r="21">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>167.4794510227642</v>
+        <v>166.1440209330802</v>
       </c>
     </row>
     <row r="22">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="F22">
-        <v>186.9982104740173</v>
+        <v>184.9702062347645</v>
       </c>
     </row>
     <row r="23">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>225.3546129222136</v>
+        <v>223.1646542193233</v>
       </c>
     </row>
     <row r="24">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>191.7877356995985</v>
+        <v>189.5638131056606</v>
       </c>
     </row>
     <row r="25">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>218.9174969863301</v>
+        <v>216.8427155394305</v>
       </c>
     </row>
     <row r="26">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>247.5484616980287</v>
+        <v>244.9677433454393</v>
       </c>
     </row>
     <row r="27">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>277.5001470091651</v>
+        <v>274.7406237796313</v>
       </c>
     </row>
     <row r="28">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>273.1911041451213</v>
+        <v>269.5024230922737</v>
       </c>
     </row>
     <row r="29">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>278.7329514534464</v>
+        <v>275.4331363625215</v>
       </c>
     </row>
     <row r="30">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>271.5517565693888</v>
+        <v>269.1750144168849</v>
       </c>
     </row>
     <row r="31">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>258.9032181470266</v>
+        <v>255.6514551452244</v>
       </c>
     </row>
     <row r="32">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>187.0072808078066</v>
+        <v>185.4158425590985</v>
       </c>
     </row>
     <row r="33">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>232.1081678656959</v>
+        <v>229.7314483656197</v>
       </c>
     </row>
     <row r="34">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>266.4149295467641</v>
+        <v>263.4621234459282</v>
       </c>
     </row>
     <row r="35">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>288.332705631062</v>
+        <v>285.7620598900472</v>
       </c>
     </row>
     <row r="36">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>243.6553601063086</v>
+        <v>239.8075953045548</v>
       </c>
     </row>
     <row r="37">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>304.5908127096516</v>
+        <v>301.0712549856906</v>
       </c>
     </row>
     <row r="38">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>259.0578649060102</v>
+        <v>255.7715174652351</v>
       </c>
     </row>
     <row r="39">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>298.9562267566762</v>
+        <v>295.6425687789092</v>
       </c>
     </row>
     <row r="40">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>243.5505142898121</v>
+        <v>241.17288825842</v>
       </c>
     </row>
     <row r="41">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>297.4423121853187</v>
+        <v>295.0663872863947</v>
       </c>
     </row>
     <row r="42">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>241.5333798480976</v>
+        <v>238.085987319424</v>
       </c>
     </row>
     <row r="43">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>276.1384995678744</v>
+        <v>273.0808506327567</v>
       </c>
     </row>
     <row r="44">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>176.4326739840571</v>
+        <v>174.8198180184403</v>
       </c>
     </row>
     <row r="45">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>197.0710942619934</v>
+        <v>195.5000391737348</v>
       </c>
     </row>
     <row r="46">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>210.6214011523071</v>
+        <v>208.3358244354318</v>
       </c>
     </row>
     <row r="47">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>253.7844798156433</v>
+        <v>251.315813517475</v>
       </c>
     </row>
     <row r="48">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>231.0834009087349</v>
+        <v>228.4132132611975</v>
       </c>
     </row>
     <row r="49">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>263.7971659253734</v>
+        <v>261.3047412104219</v>
       </c>
     </row>
     <row r="50">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>198.4147578321731</v>
+        <v>196.3283201315369</v>
       </c>
     </row>
     <row r="51">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>221.8260445142896</v>
+        <v>219.5870883276022</v>
       </c>
     </row>
     <row r="52">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>224.9337516464444</v>
+        <v>221.891355958039</v>
       </c>
     </row>
     <row r="53">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>230.1741136826712</v>
+        <v>227.4443354579907</v>
       </c>
     </row>
     <row r="54">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="F54">
-        <v>229.3846627839536</v>
+        <v>227.3717005770906</v>
       </c>
     </row>
     <row r="55">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>201.2230953542665</v>
+        <v>198.6952364618872</v>
       </c>
     </row>
     <row r="56">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="F56">
-        <v>138.7890091962096</v>
+        <v>137.6065079097973</v>
       </c>
     </row>
     <row r="57">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>194.3608927603723</v>
+        <v>192.370710326349</v>
       </c>
     </row>
     <row r="58">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F58">
-        <v>213.1958780234546</v>
+        <v>210.7923955589661</v>
       </c>
     </row>
     <row r="59">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="F59">
-        <v>230.2595086971783</v>
+        <v>228.1813288376291</v>
       </c>
     </row>
     <row r="60">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F60">
-        <v>201.0120052063976</v>
+        <v>197.8311212710588</v>
       </c>
     </row>
     <row r="61">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F61">
-        <v>250.3651701197706</v>
+        <v>247.4700025014494</v>
       </c>
     </row>
     <row r="62">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F62">
-        <v>213.9340093386497</v>
+        <v>211.2158917281409</v>
       </c>
     </row>
     <row r="63">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="F63">
-        <v>246.8667010474335</v>
+        <v>244.1249373196631</v>
       </c>
     </row>
     <row r="64">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F64">
-        <v>206.0081595397197</v>
+        <v>203.9954485748985</v>
       </c>
     </row>
     <row r="65">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="F65">
-        <v>250.9990844338183</v>
+        <v>248.9858899231169</v>
       </c>
     </row>
     <row r="66">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="F66">
-        <v>187.7408159714768</v>
+        <v>185.0608151930446</v>
       </c>
     </row>
     <row r="67">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="F67">
-        <v>214.6009331532056</v>
+        <v>212.2240375672713</v>
       </c>
     </row>
     <row r="68">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>130.9176177733322</v>
+        <v>129.7192194532765</v>
       </c>
     </row>
     <row r="69">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="F69">
-        <v>146.2801827428997</v>
+        <v>145.1128106034837</v>
       </c>
     </row>
     <row r="70">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="F70">
-        <v>176.4305397891598</v>
+        <v>174.515202287653</v>
       </c>
     </row>
     <row r="71">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="F71">
-        <v>212.4494181100004</v>
+        <v>210.3837304998499</v>
       </c>
     </row>
     <row r="72">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="F72">
-        <v>185.3098393960044</v>
+        <v>183.1475130922329</v>
       </c>
     </row>
     <row r="73">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>211.3474731326388</v>
+        <v>209.3359268327903</v>
       </c>
     </row>
     <row r="74">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="F74">
-        <v>239.3690815816242</v>
+        <v>236.860944147654</v>
       </c>
     </row>
     <row r="75">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>276.9776295916038</v>
+        <v>274.223051081587</v>
       </c>
     </row>
     <row r="76">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>273.1706143819874</v>
+        <v>269.4821244450572</v>
       </c>
     </row>
     <row r="77">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="F77">
-        <v>278.5014797052831</v>
+        <v>275.2043797979399</v>
       </c>
     </row>
     <row r="78">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>265.0785773807465</v>
+        <v>262.7570285100408</v>
       </c>
     </row>
     <row r="79">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F79">
-        <v>258.9032181470266</v>
+        <v>255.6514551452244</v>
       </c>
     </row>
     <row r="80">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>163.3368287992505</v>
+        <v>161.945669097166</v>
       </c>
     </row>
     <row r="81">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>218.7374009283901</v>
+        <v>216.4958888059315</v>
       </c>
     </row>
     <row r="82">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>265.9182897247678</v>
+        <v>262.9708584960798</v>
       </c>
     </row>
     <row r="83">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="F83">
-        <v>287.7849004307477</v>
+        <v>285.218779060835</v>
       </c>
     </row>
     <row r="84">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>243.6370413721139</v>
+        <v>239.7894550865362</v>
       </c>
     </row>
     <row r="85">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>304.568014906609</v>
+        <v>301.0486616934608</v>
       </c>
     </row>
     <row r="86">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>258.8353836172741</v>
+        <v>255.5516981165323</v>
       </c>
     </row>
     <row r="87">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>298.7155140562228</v>
+        <v>295.4046259890615</v>
       </c>
     </row>
     <row r="88">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>237.4804903442172</v>
+        <v>235.1588221219212</v>
       </c>
     </row>
     <row r="89">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>290.596366919452</v>
+        <v>288.2749284038134</v>
       </c>
     </row>
     <row r="90">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>241.5333798480976</v>
+        <v>238.085987319424</v>
       </c>
     </row>
     <row r="91">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>276.1384995678744</v>
+        <v>273.0808506327567</v>
       </c>
     </row>
     <row r="92">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>154.1101100305656</v>
+        <v>152.7001533207365</v>
       </c>
     </row>
     <row r="93">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>172.1178622721679</v>
+        <v>170.7445916115006</v>
       </c>
     </row>
     <row r="94">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>198.575761608398</v>
+        <v>196.4187839316089</v>
       </c>
     </row>
     <row r="95">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>239.0768958906612</v>
+        <v>236.7501036030065</v>
       </c>
     </row>
     <row r="96">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>223.5421224540177</v>
+        <v>220.9435778420213</v>
       </c>
     </row>
     <row r="97">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>254.9880690225915</v>
+        <v>252.5691507852299</v>
       </c>
     </row>
     <row r="98">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="F98">
-        <v>115.248956720007</v>
+        <v>113.9544634893662</v>
       </c>
     </row>
     <row r="99">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="F99">
-        <v>122.7187063431167</v>
+        <v>121.4164502649449</v>
       </c>
     </row>
     <row r="100">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="F100">
-        <v>122.8088409401229</v>
+        <v>121.1556420067288</v>
       </c>
     </row>
     <row r="101">
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="F101">
-        <v>130.9315604456168</v>
+        <v>129.2229185480618</v>
       </c>
     </row>
     <row r="102">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="F102">
-        <v>133.9226267039411</v>
+        <v>132.5907690627994</v>
       </c>
     </row>
     <row r="103">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="F103">
-        <v>109.7628570366262</v>
+        <v>108.3784613020942</v>
       </c>
     </row>
     <row r="104">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>90.30512076170933</v>
+        <v>89.43772207136922</v>
       </c>
     </row>
     <row r="105">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F105">
-        <v>120.0085446546611</v>
+        <v>118.5962400016613</v>
       </c>
     </row>
     <row r="106">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="F106">
-        <v>117.5708565163258</v>
+        <v>116.2009766688983</v>
       </c>
     </row>
     <row r="107">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="F107">
-        <v>127.7492242571382</v>
+        <v>126.5130506394304</v>
       </c>
     </row>
     <row r="108">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="F108">
-        <v>109.2299438433055</v>
+        <v>107.5373243818202</v>
       </c>
     </row>
     <row r="109">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="F109">
-        <v>137.2446855529257</v>
+        <v>135.6333949287279</v>
       </c>
     </row>
     <row r="110">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F110">
-        <v>121.5345898855326</v>
+        <v>119.8540634484984</v>
       </c>
     </row>
     <row r="111">
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="F111">
-        <v>140.590350113188</v>
+        <v>138.8528094000156</v>
       </c>
     </row>
     <row r="112">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="F112">
-        <v>120.6722382712564</v>
+        <v>119.351669691951</v>
       </c>
     </row>
     <row r="113">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F113">
-        <v>146.1742230875528</v>
+        <v>144.8319273351157</v>
       </c>
     </row>
     <row r="114">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="F114">
-        <v>102.1818208891596</v>
+        <v>100.7335430597937</v>
       </c>
     </row>
     <row r="115">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="F115">
-        <v>117.2851660653326</v>
+        <v>115.9641575577435</v>
       </c>
     </row>
     <row r="116">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F116">
-        <v>85.18243625305477</v>
+        <v>84.31080393560521</v>
       </c>
     </row>
     <row r="117">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="F117">
-        <v>95.18036029912312</v>
+        <v>94.31699073574478</v>
       </c>
     </row>
     <row r="118">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="F118">
-        <v>108.9281787913259</v>
+        <v>107.5791896356873</v>
       </c>
     </row>
     <row r="119">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="F119">
-        <v>131.1866558231301</v>
+        <v>129.7104771359219</v>
       </c>
     </row>
     <row r="120">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F120">
-        <v>107.379733067185</v>
+        <v>106.0634678045901</v>
       </c>
     </row>
     <row r="121">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="F121">
-        <v>123.0147760674015</v>
+        <v>121.7417687767268</v>
       </c>
     </row>
     <row r="122">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="F122">
-        <v>138.7728710228168</v>
+        <v>137.2199521231041</v>
       </c>
     </row>
     <row r="123">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="F123">
-        <v>153.2898984319826</v>
+        <v>151.6817392654643</v>
       </c>
     </row>
     <row r="124">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="F124">
-        <v>149.1601803663034</v>
+        <v>147.1553419669008</v>
       </c>
     </row>
     <row r="125">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="F125">
-        <v>158.286327158709</v>
+        <v>156.225414821453</v>
       </c>
     </row>
     <row r="126">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="F126">
-        <v>154.4085958545948</v>
+        <v>152.8777823593116</v>
       </c>
     </row>
     <row r="127">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F127">
-        <v>141.2307805052833</v>
+        <v>139.4497514624218</v>
       </c>
     </row>
     <row r="128">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F128">
-        <v>106.2776397891987</v>
+        <v>105.2572493082924</v>
       </c>
     </row>
     <row r="129">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="F129">
-        <v>135.1709842672249</v>
+        <v>133.5787943795237</v>
       </c>
     </row>
     <row r="130">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="F130">
-        <v>146.7102227321197</v>
+        <v>145.0237877440875</v>
       </c>
     </row>
     <row r="131">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="F131">
-        <v>159.7196074542528</v>
+        <v>158.1879400144952</v>
       </c>
     </row>
     <row r="132">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="F132">
-        <v>132.4143096113699</v>
+        <v>130.3661321501819</v>
       </c>
     </row>
     <row r="133">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F133">
-        <v>166.9628624545986</v>
+        <v>165.0040981919341</v>
       </c>
     </row>
     <row r="134">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="F134">
-        <v>146.9109535373512</v>
+        <v>144.8835713991253</v>
       </c>
     </row>
     <row r="135">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="F135">
-        <v>169.9786423039139</v>
+        <v>167.8832655466761</v>
       </c>
     </row>
     <row r="136">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="F136">
-        <v>138.7940916084226</v>
+        <v>137.2760450220967</v>
       </c>
     </row>
     <row r="137">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="F137">
-        <v>168.8461049680941</v>
+        <v>167.303486912031</v>
       </c>
     </row>
     <row r="138">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F138">
-        <v>131.4641876879074</v>
+        <v>129.6010277609471</v>
       </c>
     </row>
     <row r="139">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="F139">
-        <v>150.9217156097676</v>
+        <v>149.2221812173699</v>
       </c>
     </row>
     <row r="140">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>100.2716361562998</v>
+        <v>99.24621136242902</v>
       </c>
     </row>
     <row r="141">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="F141">
-        <v>111.9935308075682</v>
+        <v>110.977931463334</v>
       </c>
     </row>
     <row r="142">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="F142">
-        <v>122.703253176281</v>
+        <v>121.1824765497022</v>
       </c>
     </row>
     <row r="143">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F143">
-        <v>147.748699287836</v>
+        <v>146.0844661678465</v>
       </c>
     </row>
     <row r="144">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="F144">
-        <v>129.2893964793354</v>
+        <v>127.7106199219366</v>
       </c>
     </row>
     <row r="145">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="F145">
-        <v>148.1317294489447</v>
+        <v>146.6043284284017</v>
       </c>
     </row>
   </sheetData>
